--- a/research/traditional_assets/database/data/tanzania/tanzania_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/tanzania/tanzania_financial_svcs_non_bank_insurance.xlsx
@@ -588,40 +588,40 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.3312693498452012</v>
+        <v>0.1571917808219178</v>
       </c>
       <c r="H2">
-        <v>0.3312693498452012</v>
+        <v>0.1571917808219178</v>
       </c>
       <c r="I2">
-        <v>0.3058823529411765</v>
+        <v>0.2462328767123288</v>
       </c>
       <c r="J2">
-        <v>0.2952429667519182</v>
+        <v>0.2409912857724129</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="L2">
-        <v>0.6191950464396285</v>
+        <v>0.678082191780822</v>
       </c>
       <c r="M2">
-        <v>0.765</v>
+        <v>0.978</v>
       </c>
       <c r="N2">
-        <v>0.05708955223880597</v>
+        <v>0.05620689655172414</v>
       </c>
       <c r="O2">
-        <v>0.3825</v>
+        <v>0.493939393939394</v>
       </c>
       <c r="P2">
-        <v>0.765</v>
+        <v>0.978</v>
       </c>
       <c r="Q2">
-        <v>0.05708955223880597</v>
+        <v>0.05620689655172414</v>
       </c>
       <c r="R2">
-        <v>0.3825</v>
+        <v>0.493939393939394</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,31 +630,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.093</v>
+        <v>0.089</v>
       </c>
       <c r="V2">
-        <v>0.006940298507462687</v>
+        <v>0.005114942528735632</v>
       </c>
       <c r="W2">
-        <v>0.2081165452653486</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="X2">
-        <v>0.03360415921485008</v>
+        <v>0.06311951548698429</v>
       </c>
       <c r="Y2">
-        <v>0.1745123860504985</v>
+        <v>0.120213817846349</v>
       </c>
       <c r="Z2">
-        <v>0.3389296956977965</v>
+        <v>0.2715773809523809</v>
       </c>
       <c r="AA2">
-        <v>0.1000666088781423</v>
+        <v>0.06544778222241866</v>
       </c>
       <c r="AB2">
-        <v>0.03360415921485008</v>
+        <v>0.06311951548698429</v>
       </c>
       <c r="AC2">
-        <v>0.06646244966329218</v>
+        <v>0.002328266735434376</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.093</v>
+        <v>-0.089</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -675,25 +675,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.006988802885699256</v>
+        <v>-0.005141239674195598</v>
       </c>
       <c r="AK2">
-        <v>-0.008685906416363126</v>
+        <v>-0.007665145121005943</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.04</v>
+        <v>-1.26</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.08691588785046728</v>
+        <v>-0.1209239130434783</v>
       </c>
       <c r="AQ2">
-        <v>-0.95</v>
+        <v>-0.5706349206349206</v>
       </c>
     </row>
     <row r="3">
@@ -713,40 +713,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.3312693498452012</v>
+        <v>0.1571917808219178</v>
       </c>
       <c r="H3">
-        <v>0.3312693498452012</v>
+        <v>0.1571917808219178</v>
       </c>
       <c r="I3">
-        <v>0.3058823529411765</v>
+        <v>0.2462328767123288</v>
       </c>
       <c r="J3">
-        <v>0.2952429667519182</v>
+        <v>0.2409912857724129</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="L3">
-        <v>0.6191950464396285</v>
+        <v>0.678082191780822</v>
       </c>
       <c r="M3">
-        <v>0.765</v>
+        <v>0.978</v>
       </c>
       <c r="N3">
-        <v>0.05708955223880597</v>
+        <v>0.05620689655172414</v>
       </c>
       <c r="O3">
-        <v>0.3825</v>
+        <v>0.493939393939394</v>
       </c>
       <c r="P3">
-        <v>0.765</v>
+        <v>0.978</v>
       </c>
       <c r="Q3">
-        <v>0.05708955223880597</v>
+        <v>0.05620689655172414</v>
       </c>
       <c r="R3">
-        <v>0.3825</v>
+        <v>0.493939393939394</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -755,31 +755,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.093</v>
+        <v>0.089</v>
       </c>
       <c r="V3">
-        <v>0.006940298507462687</v>
+        <v>0.005114942528735632</v>
       </c>
       <c r="W3">
-        <v>0.2081165452653486</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="X3">
-        <v>0.03360415921485008</v>
+        <v>0.06311951548698429</v>
       </c>
       <c r="Y3">
-        <v>0.1745123860504985</v>
+        <v>0.120213817846349</v>
       </c>
       <c r="Z3">
-        <v>0.3389296956977965</v>
+        <v>0.2715773809523809</v>
       </c>
       <c r="AA3">
-        <v>0.1000666088781423</v>
+        <v>0.06544778222241866</v>
       </c>
       <c r="AB3">
-        <v>0.03360415921485008</v>
+        <v>0.06311951548698429</v>
       </c>
       <c r="AC3">
-        <v>0.06646244966329218</v>
+        <v>0.002328266735434376</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -791,7 +791,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.093</v>
+        <v>-0.089</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -800,25 +800,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.006988802885699256</v>
+        <v>-0.005141239674195598</v>
       </c>
       <c r="AK3">
-        <v>-0.008685906416363126</v>
+        <v>-0.007665145121005943</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1.04</v>
+        <v>-1.26</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.08691588785046728</v>
+        <v>-0.1209239130434783</v>
       </c>
       <c r="AQ3">
-        <v>-0.95</v>
+        <v>-0.5706349206349206</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/tanzania/tanzania_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/tanzania/tanzania_financial_svcs_non_bank_insurance.xlsx
@@ -587,41 +587,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.176</v>
+      </c>
+      <c r="E2">
+        <v>0.0392</v>
+      </c>
       <c r="G2">
-        <v>0.1571917808219178</v>
+        <v>0.4481927710843374</v>
       </c>
       <c r="H2">
-        <v>0.1571917808219178</v>
+        <v>0.4481927710843374</v>
       </c>
       <c r="I2">
-        <v>0.2462328767123288</v>
+        <v>0.4337349397590361</v>
       </c>
       <c r="J2">
-        <v>0.2409912857724129</v>
+        <v>0.4266139183600072</v>
       </c>
       <c r="K2">
         <v>1.98</v>
       </c>
       <c r="L2">
-        <v>0.678082191780822</v>
+        <v>0.4771084337349397</v>
       </c>
       <c r="M2">
-        <v>0.978</v>
+        <v>1.19</v>
       </c>
       <c r="N2">
-        <v>0.05620689655172414</v>
+        <v>0.0695906432748538</v>
       </c>
       <c r="O2">
-        <v>0.493939393939394</v>
+        <v>0.6010101010101011</v>
       </c>
       <c r="P2">
-        <v>0.978</v>
+        <v>1.19</v>
       </c>
       <c r="Q2">
-        <v>0.05620689655172414</v>
+        <v>0.0695906432748538</v>
       </c>
       <c r="R2">
-        <v>0.493939393939394</v>
+        <v>0.6010101010101011</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.089</v>
+        <v>0.038</v>
       </c>
       <c r="V2">
-        <v>0.005114942528735632</v>
+        <v>0.002222222222222222</v>
       </c>
       <c r="W2">
-        <v>0.1833333333333333</v>
+        <v>0.1752212389380531</v>
       </c>
       <c r="X2">
-        <v>0.06311951548698429</v>
+        <v>0.06908412471788317</v>
       </c>
       <c r="Y2">
-        <v>0.120213817846349</v>
+        <v>0.1061371142201699</v>
       </c>
       <c r="Z2">
-        <v>0.2715773809523809</v>
+        <v>0.3683976919662672</v>
       </c>
       <c r="AA2">
-        <v>0.06544778222241866</v>
+        <v>0.1571635828845122</v>
       </c>
       <c r="AB2">
-        <v>0.06311951548698429</v>
+        <v>0.06908412471788317</v>
       </c>
       <c r="AC2">
-        <v>0.002328266735434376</v>
+        <v>0.08807945816662902</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.089</v>
+        <v>-0.038</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -675,25 +681,22 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.005141239674195598</v>
+        <v>-0.0022271714922049</v>
       </c>
       <c r="AK2">
-        <v>-0.007665145121005943</v>
+        <v>-0.003124486104259168</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.26</v>
+        <v>0</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.1209239130434783</v>
-      </c>
-      <c r="AQ2">
-        <v>-0.5706349206349206</v>
+        <v>-0.02043010752688172</v>
       </c>
     </row>
     <row r="3">
@@ -712,41 +715,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.176</v>
+      </c>
+      <c r="E3">
+        <v>0.0392</v>
+      </c>
       <c r="G3">
-        <v>0.1571917808219178</v>
+        <v>0.4481927710843374</v>
       </c>
       <c r="H3">
-        <v>0.1571917808219178</v>
+        <v>0.4481927710843374</v>
       </c>
       <c r="I3">
-        <v>0.2462328767123288</v>
+        <v>0.4337349397590361</v>
       </c>
       <c r="J3">
-        <v>0.2409912857724129</v>
+        <v>0.4266139183600072</v>
       </c>
       <c r="K3">
         <v>1.98</v>
       </c>
       <c r="L3">
-        <v>0.678082191780822</v>
+        <v>0.4771084337349397</v>
       </c>
       <c r="M3">
-        <v>0.978</v>
+        <v>1.19</v>
       </c>
       <c r="N3">
-        <v>0.05620689655172414</v>
+        <v>0.0695906432748538</v>
       </c>
       <c r="O3">
-        <v>0.493939393939394</v>
+        <v>0.6010101010101011</v>
       </c>
       <c r="P3">
-        <v>0.978</v>
+        <v>1.19</v>
       </c>
       <c r="Q3">
-        <v>0.05620689655172414</v>
+        <v>0.0695906432748538</v>
       </c>
       <c r="R3">
-        <v>0.493939393939394</v>
+        <v>0.6010101010101011</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -755,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.089</v>
+        <v>0.038</v>
       </c>
       <c r="V3">
-        <v>0.005114942528735632</v>
+        <v>0.002222222222222222</v>
       </c>
       <c r="W3">
-        <v>0.1833333333333333</v>
+        <v>0.1752212389380531</v>
       </c>
       <c r="X3">
-        <v>0.06311951548698429</v>
+        <v>0.06908412471788317</v>
       </c>
       <c r="Y3">
-        <v>0.120213817846349</v>
+        <v>0.1061371142201699</v>
       </c>
       <c r="Z3">
-        <v>0.2715773809523809</v>
+        <v>0.3683976919662672</v>
       </c>
       <c r="AA3">
-        <v>0.06544778222241866</v>
+        <v>0.1571635828845122</v>
       </c>
       <c r="AB3">
-        <v>0.06311951548698429</v>
+        <v>0.06908412471788317</v>
       </c>
       <c r="AC3">
-        <v>0.002328266735434376</v>
+        <v>0.08807945816662902</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -791,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.089</v>
+        <v>-0.038</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -800,25 +809,22 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.005141239674195598</v>
+        <v>-0.0022271714922049</v>
       </c>
       <c r="AK3">
-        <v>-0.007665145121005943</v>
+        <v>-0.003124486104259168</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1.26</v>
+        <v>0</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.1209239130434783</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.5706349206349206</v>
+        <v>-0.02043010752688172</v>
       </c>
     </row>
   </sheetData>
